--- a/output/roomself_excel/5105.xlsx
+++ b/output/roomself_excel/5105.xlsx
@@ -498,10 +498,10 @@
         <v>2576</v>
       </c>
       <c r="E3" t="n">
-        <v>600</v>
+        <v>466</v>
       </c>
       <c r="F3" t="n">
-        <v>466</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         <v>2560</v>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>185</v>
       </c>
       <c r="F5" t="n">
-        <v>185</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>1452</v>
       </c>
       <c r="E6" t="n">
-        <v>600</v>
+        <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>358</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -586,7 +586,7 @@
         <v>2040</v>
       </c>
       <c r="E7" t="n">
-        <v>600</v>
+        <v>336</v>
       </c>
       <c r="F7" t="n">
         <v>236</v>

--- a/output/roomself_excel/5105.xlsx
+++ b/output/roomself_excel/5105.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,11 +540,60 @@
       <c r="D2" t="n">
         <v>8528</v>
       </c>
-      <c r="E2" t="n">
-        <v>832</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>593</v>
+        <v>232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>744</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>295</v>
+      </c>
+      <c r="M2" t="n">
+        <v>29</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>630</v>
+      </c>
+      <c r="P2" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>212</v>
+      </c>
+      <c r="S2" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +611,37 @@
       <c r="D3" t="n">
         <v>2576</v>
       </c>
-      <c r="E3" t="n">
-        <v>466</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>401</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="G3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>428</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +658,45 @@
       <c r="D4" t="n">
         <v>2532</v>
       </c>
-      <c r="E4" t="n">
-        <v>374</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>336</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>335</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +713,29 @@
       <c r="D5" t="n">
         <v>2560</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>185</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>38</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +752,29 @@
       <c r="D6" t="n">
         <v>1452</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>147</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>33</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +791,37 @@
       <c r="D7" t="n">
         <v>2040</v>
       </c>
-      <c r="E7" t="n">
-        <v>336</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>236</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>298</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +838,37 @@
       <c r="D8" t="n">
         <v>1420</v>
       </c>
-      <c r="E8" t="n">
-        <v>244</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>189</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>205</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +885,29 @@
       <c r="D9" t="n">
         <v>676</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>84</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>25</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +924,29 @@
       <c r="D10" t="n">
         <v>900</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>85</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>29</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +963,37 @@
       <c r="D11" t="n">
         <v>1796</v>
       </c>
-      <c r="E11" t="n">
-        <v>251</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>234</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>198</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
